--- a/artfynd/A 9157-2024 artfynd.xlsx
+++ b/artfynd/A 9157-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118122206</v>
+        <v>118122064</v>
       </c>
       <c r="B2" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredtjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333032</v>
+        <v>333028</v>
       </c>
       <c r="R2" t="n">
-        <v>6628910</v>
+        <v>6628913</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +766,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -822,61 +819,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118122064</v>
+        <v>118131918</v>
       </c>
       <c r="B3" t="n">
-        <v>90504</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bredtjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333028</v>
+        <v>333066</v>
       </c>
       <c r="R3" t="n">
-        <v>6628913</v>
+        <v>6628938</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,7 +901,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,44 +911,18 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -968,6 +935,148 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118122206</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bredtjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>333032</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6628910</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9157-2024 artfynd.xlsx
+++ b/artfynd/A 9157-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -816,6 +821,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118122064</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -935,6 +945,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118131918</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1077,8 +1092,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118122206</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>